--- a/Documents/Networks_Summary 1.0.xlsx
+++ b/Documents/Networks_Summary 1.0.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wopi.dropbox.com/wopi/files/oid_16786041899880003328/WOPIServiceId_TP_DROPBOX_PLUS/WOPIUserId_-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zheng\PycharmProjects\GMNS_Plus_Dataset\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{10DD960E-03AF-4C37-9D7B-27493088DB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADCDCBDF-383A-40F5-AB03-28DFA0C75305}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3137F7-E2B6-491C-8681-AC1A45867C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{CED9102F-33E9-4EFE-880B-5D1E6F03019D}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CED9102F-33E9-4EFE-880B-5D1E6F03019D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="0501" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="110">
   <si>
     <t xml:space="preserve">vdf_fftt </t>
   </si>
@@ -198,17 +199,208 @@
   <si>
     <t>original unit feet</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <t>free speed</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>TNTP Dataset https://github.com/bstabler/TransportationNetworks</t>
+  </si>
+  <si>
+    <t>Anaheim</t>
+  </si>
+  <si>
+    <t>Berlin-Center</t>
+  </si>
+  <si>
+    <t>Berlin-Friedrichshain</t>
+  </si>
+  <si>
+    <t>Berlin-Mitte-Center</t>
+  </si>
+  <si>
+    <t>Berlin-Mitte-Prenzlauerberg-Friedrichshain-Center</t>
+  </si>
+  <si>
+    <t>Berlin-Prenzlauerberg-Center</t>
+  </si>
+  <si>
+    <t>Berlin-Tiergarten</t>
+  </si>
+  <si>
+    <t>Birmingham-England</t>
+  </si>
+  <si>
+    <t>Chicago_Regional</t>
+  </si>
+  <si>
+    <t>Chicago_Sketch</t>
+  </si>
+  <si>
+    <t>GoldCoast</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
+  </si>
+  <si>
+    <t>Sioux_Falls</t>
+  </si>
+  <si>
+    <t>Sydney</t>
+  </si>
+  <si>
+    <t>Bay_Area_MultiModal</t>
+  </si>
+  <si>
+    <t>King_County_MultiModal</t>
+  </si>
+  <si>
+    <t>Phoenix_MultiModal</t>
+  </si>
+  <si>
+    <t>WashingtonDC_MultiModal</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Bay_Area_Driving</t>
+  </si>
+  <si>
+    <t>Bay_Area_Biking</t>
+  </si>
+  <si>
+    <t>Bay_Area_Walking</t>
+  </si>
+  <si>
+    <t>Bay_Area_Transit</t>
+  </si>
+  <si>
+    <t>King_County_Driving</t>
+  </si>
+  <si>
+    <t>Phoenix_Driving</t>
+  </si>
+  <si>
+    <t>WashingtonDC_Driving</t>
+  </si>
+  <si>
+    <t>King_County_Biking</t>
+  </si>
+  <si>
+    <t>Phoenix_Biking</t>
+  </si>
+  <si>
+    <t>WashingtonDC_Biking</t>
+  </si>
+  <si>
+    <t>King_County_Walking</t>
+  </si>
+  <si>
+    <t>Phoenix_Walking</t>
+  </si>
+  <si>
+    <t>WashingtonDC_Walking</t>
+  </si>
+  <si>
+    <t>King_County_Transit</t>
+  </si>
+  <si>
+    <t>Phoenix_Transit</t>
+  </si>
+  <si>
+    <t>WashingtonDC_Transit</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> General Modeling Network Specification (GMNS) https://github.com/zephyr-data-specs/GMNS</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>Boston</t>
+  </si>
+  <si>
+    <t>Chicago_Downtown</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>Denver</t>
+  </si>
+  <si>
+    <t>Honolulu</t>
+  </si>
+  <si>
+    <t>Las_Vegas</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>Milwaukee</t>
+  </si>
+  <si>
+    <t>Minneapolis</t>
+  </si>
+  <si>
+    <t>New_Orleans</t>
+  </si>
+  <si>
+    <t>New_York</t>
+  </si>
+  <si>
+    <t>Phoenix_city</t>
+  </si>
+  <si>
+    <t>Pittsburgh</t>
+  </si>
+  <si>
+    <t>Portland</t>
+  </si>
+  <si>
+    <t>San_Francisco</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>WashingtonDC</t>
+  </si>
+  <si>
+    <t>Driving, Biking, Walking Networks are Generated from OpenStreetMap by OSM2GMNS https://osm2gmns.readthedocs.io/en/stable/. 
+Transit Networks are Generated from GTFS dataset by GTFS2GMNS https://github.com/asu-trans-ai-lab/GTFS2GMNS</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>USTA20
+Xu, X., Zheng, Z., Hu, Z. et al. A unified dataset for the city-scale traffic assignment model in 20 U.S. cities. Sci Data 11, 325 (2024). https://doi.org/10.1038/s41597-024-03149-8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -216,23 +408,41 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -287,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -300,6 +510,29 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -747,19 +980,1265 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1E24EB6-A3F2-453F-8FA7-54AD9E1C0052}">
+  <dimension ref="C4:J58"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="6" width="36.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C5" s="17">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C6" s="19">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C7" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C8" s="19">
+        <v>1.3</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C9" s="19">
+        <v>1.4</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C10" s="18">
+        <v>2</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C11" s="19">
+        <v>2.1</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C12" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C13" s="19">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C14" s="19">
+        <v>2.4</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C15" s="18">
+        <v>3</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C16" s="19">
+        <v>3.1</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C17" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C18" s="19">
+        <v>3.3</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C19" s="19">
+        <v>3.4</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C20" s="18">
+        <v>4</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C21" s="19">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C22" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C23" s="19">
+        <v>4.3</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C24" s="19">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C25" s="20">
+        <v>5</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="15"/>
+      <c r="G25" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C26" s="20">
+        <v>6</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="16"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C27" s="20">
+        <v>7</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C28" s="20">
+        <v>8</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C29" s="20">
+        <v>9</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="16"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C30" s="20">
+        <v>10</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="16"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C31" s="20">
+        <v>11</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C32" s="20">
+        <v>12</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C33" s="20">
+        <v>13</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C34" s="20">
+        <v>14</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="16"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C35" s="20">
+        <v>15</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="16"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C36" s="20">
+        <v>16</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="16"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C37" s="20">
+        <v>17</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" s="16"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C38" s="20">
+        <v>18</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="16"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C39" s="18">
+        <v>19</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="F39" s="15"/>
+      <c r="G39" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C40" s="18">
+        <v>20</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C41" s="18">
+        <v>21</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C42" s="18">
+        <v>22</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C43" s="18">
+        <v>23</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C44" s="18">
+        <v>24</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C45" s="18">
+        <v>25</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C46" s="18">
+        <v>26</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C47" s="18">
+        <v>27</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C48" s="18">
+        <v>28</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C49" s="18">
+        <v>29</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C50" s="18">
+        <v>30</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C51" s="18">
+        <v>31</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J51" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C52" s="18">
+        <v>32</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C53" s="18">
+        <v>33</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C54" s="18">
+        <v>34</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C55" s="18">
+        <v>35</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J55" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C56" s="18">
+        <v>36</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C57" s="18">
+        <v>37</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C58" s="18">
+        <v>38</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="E25:E38"/>
+    <mergeCell ref="E5:E24"/>
+    <mergeCell ref="F5:F58"/>
+    <mergeCell ref="E39:E58"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F4A16D9-E0A4-4395-9301-2E4E148866EE}">
   <dimension ref="C3:I29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.171875" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.82421875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.91015625" customWidth="1"/>
-    <col min="8" max="8" width="10.0859375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.90625" customWidth="1"/>
+    <col min="8" max="8" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="3" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
         <v>0</v>
@@ -780,7 +2259,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="4" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C4" s="9" t="s">
         <v>1</v>
       </c>
@@ -800,7 +2279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="5" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
@@ -820,7 +2299,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="6" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C6" s="9" t="s">
         <v>3</v>
       </c>
@@ -840,7 +2319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="7" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C7" s="9" t="s">
         <v>4</v>
       </c>
@@ -860,7 +2339,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="8" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C8" s="9" t="s">
         <v>5</v>
       </c>
@@ -880,7 +2359,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="9" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C9" s="9" t="s">
         <v>6</v>
       </c>
@@ -900,7 +2379,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="10" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C10" s="9" t="s">
         <v>7</v>
       </c>
@@ -920,7 +2399,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="11" spans="3:9" ht="15" x14ac:dyDescent="0.35">
       <c r="C11" s="8" t="s">
         <v>8</v>
       </c>
@@ -940,7 +2419,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="12" spans="3:9" ht="15" x14ac:dyDescent="0.35">
       <c r="C12" s="8" t="s">
         <v>29</v>
       </c>
@@ -960,7 +2439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="13" spans="3:9" ht="15" x14ac:dyDescent="0.35">
       <c r="C13" s="8" t="s">
         <v>10</v>
       </c>
@@ -980,7 +2459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="14" spans="3:9" ht="15" x14ac:dyDescent="0.35">
       <c r="C14" s="8" t="s">
         <v>11</v>
       </c>
@@ -1000,7 +2479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="15" spans="3:9" ht="15" x14ac:dyDescent="0.35">
       <c r="C15" s="8" t="s">
         <v>12</v>
       </c>
@@ -1020,7 +2499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="16" spans="3:9" ht="15" x14ac:dyDescent="0.35">
       <c r="C16" s="8" t="s">
         <v>13</v>
       </c>
@@ -1040,7 +2519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="17" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C17" s="9" t="s">
         <v>14</v>
       </c>
@@ -1060,7 +2539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="18" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C18" s="9" t="s">
         <v>15</v>
       </c>
@@ -1080,7 +2559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="19" spans="3:9" ht="15" x14ac:dyDescent="0.35">
       <c r="C19" s="6" t="s">
         <v>27</v>
       </c>
@@ -1103,7 +2582,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="20" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C20" s="7" t="s">
         <v>33</v>
       </c>
@@ -1126,7 +2605,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="21" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C21" s="7" t="s">
         <v>35</v>
       </c>
@@ -1149,7 +2628,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="22" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C22" s="7" t="s">
         <v>39</v>
       </c>
@@ -1172,7 +2651,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="23" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C23" s="7" t="s">
         <v>40</v>
       </c>
@@ -1195,7 +2674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="24" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C24" s="7" t="s">
         <v>42</v>
       </c>
@@ -1218,7 +2697,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="25" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C25" s="7" t="s">
         <v>44</v>
       </c>
@@ -1241,7 +2720,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="26" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C26" s="7" t="s">
         <v>45</v>
       </c>
@@ -1264,7 +2743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.65">
+    <row r="29" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
         <v>26</v>
       </c>
@@ -1275,20 +2754,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15DE6731-4DEA-40E4-8E55-25F5D5EAC5FA}">
   <dimension ref="C3:H20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.171875" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.82421875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.0859375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.0859375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
         <v>0</v>
@@ -1306,7 +2785,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1326,7 +2805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1346,7 +2825,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1366,7 +2845,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="7" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1386,7 +2865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="8" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C8" s="1" t="s">
         <v>5</v>
       </c>
@@ -1406,7 +2885,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="9" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
@@ -1426,7 +2905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1446,7 +2925,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="11" spans="3:8" ht="15" x14ac:dyDescent="0.35">
       <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
@@ -1466,7 +2945,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="3:8" ht="57" x14ac:dyDescent="0.65">
+    <row r="12" spans="3:8" ht="58" x14ac:dyDescent="0.35">
       <c r="C12" s="4" t="s">
         <v>9</v>
       </c>
@@ -1486,7 +2965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="13" spans="3:8" ht="15" x14ac:dyDescent="0.35">
       <c r="C13" s="4" t="s">
         <v>10</v>
       </c>
@@ -1506,7 +2985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="14" spans="3:8" ht="15" x14ac:dyDescent="0.35">
       <c r="C14" s="4" t="s">
         <v>11</v>
       </c>
@@ -1526,7 +3005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="3:8" ht="28.5" x14ac:dyDescent="0.65">
+    <row r="15" spans="3:8" ht="29" x14ac:dyDescent="0.35">
       <c r="C15" s="4" t="s">
         <v>12</v>
       </c>
@@ -1546,7 +3025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="16" spans="3:8" ht="15" x14ac:dyDescent="0.35">
       <c r="C16" s="4" t="s">
         <v>13</v>
       </c>
@@ -1566,7 +3045,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="17" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1586,7 +3065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="18" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C18" s="1" t="s">
         <v>15</v>
       </c>
@@ -1606,7 +3085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.65">
+    <row r="20" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
         <v>26</v>
       </c>
